--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T07:43:32+00:00</t>
+    <t>2026-04-23T15:04:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:04:42+00:00</t>
+    <t>2026-04-24T10:09:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T10:09:31+00:00</t>
+    <t>2026-04-29T08:07:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:07:00+00:00</t>
+    <t>2026-04-29T10:02:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T10:02:59+00:00</t>
+    <t>2026-04-29T14:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:00:00+00:00</t>
+    <t>2026-04-30T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:38:36+00:00</t>
+    <t>2026-05-04T08:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:17:52+00:00</t>
+    <t>2026-05-11T07:33:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T07:33:10+00:00</t>
+    <t>2026-05-11T09:19:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T09:19:17+00:00</t>
+    <t>2026-05-11T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T14:08:41+00:00</t>
+    <t>2026-05-11T15:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:21:10+00:00</t>
+    <t>2026-05-19T13:50:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T13:50:07+00:00</t>
+    <t>2026-05-20T09:40:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:40:51+00:00</t>
+    <t>2026-05-20T12:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T12:28:13+00:00</t>
+    <t>2026-06-04T12:32:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
